--- a/metodologia_cidades_inteligentes/resultados/Ranking_Representatividade_raiz_peso.xlsx
+++ b/metodologia_cidades_inteligentes/resultados/Ranking_Representatividade_raiz_peso.xlsx
@@ -2068,7 +2068,7 @@
     <t>0.29009238367584533</t>
   </si>
   <si>
-    <t>262.51067283565936</t>
+    <t>262.5106728356594</t>
   </si>
   <si>
     <t>156</t>
